--- a/veikkaus_geneva_odds.xlsx
+++ b/veikkaus_geneva_odds.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,10 +468,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="D3" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="4">
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="D4" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="5">
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="7">
@@ -540,82 +540,82 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jenson Brooksby</t>
+          <t>Adrian Mannarino</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Casper Ruud</t>
+          <t>Raphael Collignon</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.6</v>
+        <v>8.1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Adrian Mannarino</t>
+          <t>Nishesh Basavareddy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Raphael Collignon</t>
+          <t>Jaume Munar</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8.1</v>
+        <v>2.46</v>
       </c>
       <c r="D9" t="n">
-        <v>1.06</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Laslo Djere</t>
+          <t>Jenson Brooksby</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Juan Manuel Cerundolo</t>
+          <t>Casper Ruud</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.96</v>
+        <v>5.6</v>
       </c>
       <c r="D10" t="n">
-        <v>1.78</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nishesh Basavareddy</t>
+          <t>Laslo Djere</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jaume Munar</t>
+          <t>Juan Manuel Cerundolo</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.46</v>
+        <v>1.96</v>
       </c>
       <c r="D11" t="n">
-        <v>1.51</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="12">
@@ -634,6 +634,24 @@
       </c>
       <c r="D12" t="n">
         <v>1.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Stefanos Tsitsipas</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Learner Tien</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.44</v>
       </c>
     </row>
   </sheetData>
